--- a/artfynd/S 1001-2023 artfynd.xlsx
+++ b/artfynd/S 1001-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98348760</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -934,6 +944,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/191943</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,6 +1051,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/186142</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1140,6 +1160,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/72820300</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,6 +1275,11 @@
       <c r="AY6" t="inlineStr">
         <is>
           <t>Tommy Knutsson - Import Fynddatabas 2013</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/404578</t>
         </is>
       </c>
     </row>
@@ -1388,6 +1418,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/406470</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125816387</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1611,6 +1651,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/367456</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1722,6 +1767,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/458604</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1858,6 +1908,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/610335</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1959,6 +2014,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98348782</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2080,6 +2140,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/98348785</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2206,6 +2271,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2215086</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2321,6 +2391,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126643085</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2427,6 +2502,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2155796</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2523,6 +2603,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2158240</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2619,6 +2704,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2158743</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2730,6 +2820,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2207952</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2838,6 +2933,11 @@
       <c r="AY20" t="inlineStr">
         <is>
           <t>Inventering av Ölands kärlväxtflora.</t>
+        </is>
+      </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2209275</t>
         </is>
       </c>
     </row>
@@ -2942,6 +3042,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/93233197</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3038,6 +3143,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2926593</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3134,6 +3244,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/2313995</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3249,6 +3364,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119589</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3359,6 +3479,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119590</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3469,6 +3594,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119591</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3579,6 +3709,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119592</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3689,6 +3824,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119593</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3799,6 +3939,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119594</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3909,6 +4054,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119595</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4019,6 +4169,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119596</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4134,6 +4289,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119598</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4244,6 +4404,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119600</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4359,6 +4524,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119602</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4469,6 +4639,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119603</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4579,6 +4754,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119604</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4689,6 +4869,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119605</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4799,6 +4984,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119606</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4914,6 +5104,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119648</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5029,6 +5224,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119649</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5139,6 +5339,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119652</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5249,6 +5454,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119653</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5359,6 +5569,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119654</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5474,6 +5689,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119657</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5589,6 +5809,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119663</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5699,6 +5924,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119665</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5809,6 +6039,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119667</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5919,6 +6154,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119668</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -6034,6 +6274,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119669</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -6144,6 +6389,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119670</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6254,6 +6504,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119671</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6364,6 +6619,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119672</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6474,6 +6734,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119673</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6589,6 +6854,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119674</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6704,6 +6974,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119676</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6819,6 +7094,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119763</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6934,6 +7214,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119764</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -7044,6 +7329,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119765</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7159,6 +7449,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119766</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -7269,6 +7564,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119767</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7379,6 +7679,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119768</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7494,6 +7799,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119770</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7604,6 +7914,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119772</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7714,6 +8029,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119773</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7824,6 +8144,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119774</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7934,6 +8259,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119775</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -8044,6 +8374,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119794</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -8154,6 +8489,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119795</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -8264,6 +8604,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119797</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -8374,6 +8719,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119798</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8489,6 +8839,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119800</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8604,6 +8959,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119801</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8714,6 +9074,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119931</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8824,6 +9189,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119932</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8939,6 +9309,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119934</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -9054,6 +9429,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119972</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -9169,6 +9549,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119973</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -9284,6 +9669,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119974</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -9399,6 +9789,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119975</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9509,6 +9904,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119976</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9624,6 +10024,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119978</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9732,6 +10137,11 @@
       <c r="AY82" t="inlineStr">
         <is>
           <t>Skyddsvärda träd</t>
+        </is>
+      </c>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119979</t>
         </is>
       </c>
     </row>
@@ -9849,6 +10259,11 @@
           <t>Skyddsvärda träd</t>
         </is>
       </c>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106119983</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9945,6 +10360,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3388981</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -10046,6 +10466,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4949509</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -10142,6 +10567,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4952477</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -10253,6 +10683,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5301582</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -10354,6 +10789,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5303300</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10455,6 +10895,11 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/5928992</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10557,8 +11002,104 @@
           <t>Inventering av Ölands kärlväxtflora.</t>
         </is>
       </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6456639</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>